--- a/results/q3_output/表B_过载风险评估.xlsx
+++ b/results/q3_output/表B_过载风险评估.xlsx
@@ -555,7 +555,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>枣园街道</t>
+          <t>桥沟街道</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -584,7 +584,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>桥沟街道</t>
+          <t>枣园街道</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -642,7 +642,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>柳林镇</t>
+          <t>河庄坪镇</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -671,7 +671,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>河庄坪镇</t>
+          <t>姚店镇（经开区）</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -700,7 +700,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>姚店镇</t>
+          <t>万花山镇</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -729,7 +729,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>李渠镇</t>
+          <t>真武洞街道（安塞）</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -845,7 +845,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>枣园街道</t>
+          <t>桥沟街道</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -874,7 +874,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>桥沟街道</t>
+          <t>枣园街道</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -932,7 +932,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>柳林镇</t>
+          <t>河庄坪镇</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -961,7 +961,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>河庄坪镇</t>
+          <t>姚店镇（经开区）</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -990,7 +990,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>姚店镇</t>
+          <t>万花山镇</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1019,7 +1019,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>李渠镇</t>
+          <t>真武洞街道（安塞）</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
